--- a/Code/Structure Calculations.xlsx
+++ b/Code/Structure Calculations.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anarc\GitHub\TSGC-NASA_Senior_Design\Code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B785E71-2E95-45FA-8AD8-EFB8987ED2ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9942A62C-A9EB-413E-9BF1-D03F8D4B077D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="86280" yWindow="-120" windowWidth="29040" windowHeight="18240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -77,7 +77,28 @@
     <t>Axial Stress (𝜎a=pr/2t), Pa</t>
   </si>
   <si>
-    <t>Distributed Load (mg/L), kg/m</t>
+    <t>Distributed Load (mg/L), N/m</t>
+  </si>
+  <si>
+    <t>Max Deflection(m), 𝛿</t>
+  </si>
+  <si>
+    <t>Global Bending (EI = 5wL^4/384𝛿), N/m^2</t>
+  </si>
+  <si>
+    <t>Spine Stiffness (70% EI), N/m^2</t>
+  </si>
+  <si>
+    <t>Spine Inertia (EI/E)</t>
+  </si>
+  <si>
+    <t>Hoop Strain (pr/Et)*(1-v/2)</t>
+  </si>
+  <si>
+    <t>Radial Expansion (pr^2/Et)*(1-v/2), m</t>
+  </si>
+  <si>
+    <t>Axial Strain (pr/Et)*(1/2 - v)</t>
   </si>
 </sst>
 </file>
@@ -106,7 +127,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -116,6 +137,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -136,7 +163,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -417,38 +444,50 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="17" customWidth="1"/>
+    <col min="3" max="3" width="21.5703125" customWidth="1"/>
     <col min="4" max="4" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="27.42578125" customWidth="1"/>
+    <col min="6" max="6" width="40" customWidth="1"/>
     <col min="7" max="7" width="15.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B5" s="1"/>
       <c r="C5" s="2" t="s">
         <v>2</v>
@@ -456,87 +495,178 @@
       <c r="D5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="E5" s="1"/>
+      <c r="F5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="3">
         <f>(D10*D12)/D11</f>
         <v>47975000</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H5" s="1"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B6" s="1"/>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6" s="3">
         <v>8000</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="E6" s="1"/>
+      <c r="F6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="3">
         <f>(D10*D12)/(2*D11)</f>
         <v>23987500</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H6" s="1"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B7" s="1"/>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D7" s="3">
         <v>12</v>
       </c>
-      <c r="F7" t="s">
+      <c r="E7" s="1"/>
+      <c r="F7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="3">
         <f>(D6*9.81)/D7</f>
         <v>6540</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H7" s="1"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B8" s="1"/>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D8" s="3">
         <v>70000000000</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E8" s="1"/>
+      <c r="F8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8" s="3">
+        <f>(5*G7*(D7^4))/(384*D14)</f>
+        <v>88290000</v>
+      </c>
+      <c r="H8" s="1"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B9" s="1"/>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D9" s="3">
         <v>0.33</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C10" s="1" t="s">
+      <c r="E9" s="1"/>
+      <c r="F9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9" s="3">
+        <f>G8*0.7</f>
+        <v>61802999.999999993</v>
+      </c>
+      <c r="H9" s="1"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B10" s="1"/>
+      <c r="C10" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="3">
         <v>101000</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C11" s="1" t="s">
+      <c r="E10" s="1"/>
+      <c r="F10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G10" s="3">
+        <f>G9/D8</f>
+        <v>8.8289999999999994E-4</v>
+      </c>
+      <c r="H10" s="1"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B11" s="1"/>
+      <c r="C11" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="1">
+      <c r="D11" s="3">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C12" s="1" t="s">
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B12" s="1"/>
+      <c r="C12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="1">
+      <c r="D12" s="3">
         <v>2.375</v>
       </c>
+      <c r="E12" s="1"/>
+      <c r="F12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G12" s="3">
+        <f>((D10*D12)/(D8*D11))*(1-(D9/2))</f>
+        <v>5.7227321428571427E-4</v>
+      </c>
+      <c r="H12" s="1"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B13" s="1"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G13" s="3">
+        <f>((D10*D12^2)/(D8*D11))*(1-(D9/2))</f>
+        <v>1.3591488839285715E-3</v>
+      </c>
+      <c r="H13" s="1"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B14" s="1"/>
+      <c r="C14" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" s="3">
+        <f>D7/600</f>
+        <v>0.02</v>
+      </c>
+      <c r="E14" s="1"/>
+      <c r="F14" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G14" s="3">
+        <f>((D10*D12)/(D8*D11))*(0.5-D9)</f>
+        <v>1.1651071428571427E-4</v>
+      </c>
+      <c r="H14" s="1"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
